--- a/Analysis/analysis_log.xlsx
+++ b/Analysis/analysis_log.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DWH_databricks\Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C984313-0B05-4482-946B-3413EB417434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C6734B-CCF7-4072-9CA9-110DC8161BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00BC8801-F7F4-423A-B810-8E729BEDFA04}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00BC8801-F7F4-423A-B810-8E729BEDFA04}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
     <sheet name="Customers" sheetId="2" r:id="rId2"/>
+    <sheet name="Product 2016-2018" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="115">
   <si>
     <t>Stakeholder Goald</t>
   </si>
@@ -157,9 +158,6 @@
     <t>High performing products have the highest average revenue, followed by the mid and lowest performing</t>
   </si>
   <si>
-    <t>Focus strategy to incentivize the purchase of mid and higher performing products to increase revenue</t>
-  </si>
-  <si>
     <t>Recommendations</t>
   </si>
   <si>
@@ -275,6 +273,105 @@
   </si>
   <si>
     <t>Every country contributes less than 1% of revenue;however, Tong and Turkey contibution is less than 0.3%</t>
+  </si>
+  <si>
+    <t>How did revenue across all products perform during period (2015-2018)? Conduct some initial analysis to help, product, finance and marketing managers  understand high level trends</t>
+  </si>
+  <si>
+    <t>We'll use unitprice, quantity, brand,  region and purchase time columns</t>
+  </si>
+  <si>
+    <t>Slice, by brand, region country, or any other keys dimensions to surface early insights</t>
+  </si>
+  <si>
+    <t>Best performing brand is ChefChoice (~9.8M), worst performing is BrightLights (~6M)</t>
+  </si>
+  <si>
+    <t>2017 is our best performing year followed by 2016. However, revenue performance seem to range between 27.9M to 25.6M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In 2016, ChefChoice was our key revenue drivers with revenue of ~ 4.1M. </t>
+  </si>
+  <si>
+    <t>However, between the period 2017 to 2018 , Chefchoic revenue dropped from approimately ~4.1M to ~3.1M (~48%) and Soundwave dropped from ~3.1M to 2.2M</t>
+  </si>
+  <si>
+    <t>October is our overall best performing month in  the period. Maybe related to holiday promotions at that time - Thanksgiving , holloween, early-good friday</t>
+  </si>
+  <si>
+    <t>About half of the brands spiked in October - examine promotions and campaingns</t>
+  </si>
+  <si>
+    <t>Revenue/Month</t>
+  </si>
+  <si>
+    <t>Revelant Team</t>
+  </si>
+  <si>
+    <t>Bmarketing</t>
+  </si>
+  <si>
+    <t>Revenue were at an all time high in May 2016 (~2.8M), but decline every month after, followed by a slight rise in November 2016, Increasing slowly in between January 2017 to April, but had a sharpe decline again in May 2017 and rising sharply again in August 2017, fluctuated between 2M in 2018, but had a sharp decline in Aug 2018 reaching ~1.6M</t>
+  </si>
+  <si>
+    <t>ChefChoice (436K-&gt;343K),SqoundWave (456K -&gt;156k), StyleCo (334K-&gt;266K)UrbanStyle (370K-&gt;220k) were the key drivers of the dip in 2017. In 2018 the major contributors to the decline were Chefchoice (534-&gt;233), BrightLights(238-&gt;111), PeakPerformance(207-&gt;109), StyleCo(283-&gt;146) in 2018</t>
+  </si>
+  <si>
+    <t>Chefchoice is the overall best selling brand</t>
+  </si>
+  <si>
+    <t>Africa, Asia, and Europe are our major drivers of revenue</t>
+  </si>
+  <si>
+    <t>All regions revenue fluctuated during the assessment period, but Africa, Asia, and Europe all peaked simulataneously in Oct 2018. They also had a simultaneous decline in September 2017 indicating global/macro trends</t>
+  </si>
+  <si>
+    <t>While all top brands brand experienced a measurable decline, Chefchoice experienced a sharp decline from 2017 to 2018 overall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChefChoice declines occurs in the region of Africa, Europe, and Asia. Europe mainly between Nov 2017 and May 2018, Africa Aug 2017 and Jan 2018, and Asia Nov 2017 to May 2018. </t>
+  </si>
+  <si>
+    <t>Looks into these brands by region</t>
+  </si>
+  <si>
+    <t>Focus strategy to incentivize the purchase of mid and higher performing brands to increase revenue</t>
+  </si>
+  <si>
+    <t>Total revenue across 2016-2018 is ~73.4.4M, ranging in yearly revenue from ~$25.6M to ~$27.9M. Revenue dip from ~27.9M in 2017 to ~25.6M in 2018</t>
+  </si>
+  <si>
+    <t>Total order across 2016-2018 is ~3,139, ranging in yearly orders from ~1,031 to ~1,067. Orders dip from ~1067 in 2017 to ~1031 in 2018</t>
+  </si>
+  <si>
+    <t>Best performing brand is ChefChoice (385 Orders), worst performing is BrightLights (261 orders)</t>
+  </si>
+  <si>
+    <t>Product/Year</t>
+  </si>
+  <si>
+    <t>Product/Brand</t>
+  </si>
+  <si>
+    <t>Product/Month</t>
+  </si>
+  <si>
+    <t>Chefchoice, HomeComfort, StyleCo (top 3 brands by orders) had a simultaneous dip in Sep 2017 in both orders and average order value</t>
+  </si>
+  <si>
+    <t>Chefchoice, HomeComfort, StyleCo (top 3 brands by orders) had a simultaneous dip in November 2017, but contrasting rise in AVO in Nov 2017 - Likely due to purchasing of more expensive products over cheaper ones.</t>
+  </si>
+  <si>
+    <t>October is our overall best performing month in  the period. Maybe related to holiday promotions at that time - Thanksgiving , holloween, early-good Friday</t>
+  </si>
+  <si>
+    <t>Chefchoice, HomeComfort, StyleCo (top 3 brands by orders) had a simultaneous rise in Oct 2017 in Orders and Average Order Value (AOV)</t>
+  </si>
+  <si>
+    <t>Oct 2017, saw a spike in Orders in Africa and Europe over the previous month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 2017, we saw a rise of AOV in Oceania and South American over the previous month - indicating a sale of higher value products </t>
   </si>
 </sst>
 </file>
@@ -645,7 +742,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -714,7 +811,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -725,7 +822,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
@@ -747,7 +844,7 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
         <v>30</v>
@@ -758,7 +855,7 @@
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>30</v>
@@ -769,7 +866,7 @@
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
         <v>30</v>
@@ -780,7 +877,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -810,10 +907,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
         <v>80</v>
-      </c>
-      <c r="C19" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -860,7 +957,7 @@
         <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -879,7 +976,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
         <v>38</v>
@@ -890,48 +987,48 @@
         <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" t="s">
         <v>46</v>
-      </c>
-      <c r="B32" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
         <v>48</v>
-      </c>
-      <c r="B33" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +1048,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -973,7 +1070,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -984,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -992,7 +1089,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -1011,18 +1108,18 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -1030,32 +1127,32 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
-        <v>57</v>
-      </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1071,65 +1168,387 @@
         <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
         <v>69</v>
-      </c>
-      <c r="D20" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47CB2CC2-B4E6-48D1-816F-D1FE649DCCC2}">
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="23.08984375" customWidth="1"/>
+    <col min="3" max="3" width="45.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C35" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>44</v>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
